--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAB.xlsx
@@ -422,23 +422,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>33.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -453,24 +824,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>72</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F. Thomas | W. Heinz</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F. Thomas | W. Heinz</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14.9</v>
       </c>
     </row>
   </sheetData>
@@ -484,11 +971,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,32 +1033,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>F. Thomas</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Corner 3 Right</t>
         </is>
@@ -632,16 +1153,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.7</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.1</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1172,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>106</v>
+        <v>98.5</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.4</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1191,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.3</v>
+        <v>106.4</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1210,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6.4</v>
+        <v>-7.8</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.4</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1229,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -733,7 +1254,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -749,13 +1270,13 @@
         <v>0.4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -765,16 +1286,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="10">
@@ -790,7 +1311,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1</v>
@@ -809,10 +1330,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +1410,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
         </is>
       </c>
     </row>
@@ -991,7 +1512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: F. Thomas are the first perimeter names you cannot lose in help situations.</t>
+          <t>Load into F. Thomas: he is the main organizer, so make secondary creators finish possessions.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1028,12 +1549,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Priority closeouts start with F. Thomas; do not lose them in help-and-recover situations.</t>
+          <t>The main offensive references are F. Thomas and B. Ferreira; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1045,19 +1566,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from B. Ferreira and N. Sa; contest, but do not over-help into secondary advantages.</t>
+          <t>Priority closeouts start with M. Tomley, F. Thomas, and G. Silva; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Some perimeter volume comes from N. Sa and W. Heinz; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1069,31 +1590,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially F. Thomas, B. Ferreira, and W. Heinz; force them away from preferred areas.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Scoring Areas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Several players have clear comfort zones, especially F. Thomas, B. Ferreira, and W. Heinz; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: B. Ferreira | F. Thomas and F. Thomas | W. Heinz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Do not lose F. Thomas in help-and-recover situations.</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose M. Tomley and F. Thomas in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1108,23 +1653,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1238,32 +2034,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1279,37 +2075,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1325,41 +2121,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1371,41 +2167,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1422,16 +2218,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CAB_T._TONEY</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T. Toney</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1440,18 +2236,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1463,110 +2259,140 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>26</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>26.9%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.8</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>35.1%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAB_C._ROBERT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>16</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>21.6%</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>14</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>21.4%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAB_T._LISBOA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>T. Lisboa</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1584,23 +2410,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
     </row>
@@ -1620,42 +2446,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CAB_F._THOMAS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>F. Thomas</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -1664,42 +2482,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CAB_B._FERREIRA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B. Ferreira</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -1708,42 +2518,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CAB_W._HEINZ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>W. Heinz</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1752,15 +2554,15 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1768,7 +2570,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -1780,12 +2582,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1800,19 +2602,195 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>44.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>9</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>47.1%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,26 +515,26 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
@@ -567,36 +567,36 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,26 +619,26 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,41 +671,41 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -723,41 +723,41 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -775,21 +775,21 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -804,10 +804,62 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAB_C._ROBERT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -824,12 +876,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -890,16 +942,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50.5</v>
+        <v>75.7</v>
       </c>
       <c r="E2" t="n">
-        <v>81.5</v>
+        <v>89.8</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>9.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="3">
@@ -919,16 +971,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>45.7</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>80.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>65.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="G3" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -948,16 +1000,45 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45.7</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>80.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>65.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>
@@ -971,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,34 +1148,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>lineups</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (16.1 min)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (39.7 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -1153,16 +1268,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.7</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="3">
@@ -1172,16 +1287,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98.5</v>
+        <v>106.1</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -1191,16 +1306,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106.4</v>
+        <v>108.3</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -1210,16 +1325,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-7.8</v>
+        <v>-2.1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="6">
@@ -1229,16 +1344,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -1254,7 +1369,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1273,7 +1388,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1286,16 +1401,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>23.7</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1330,10 +1445,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1537,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1627,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Load into F. Thomas: he is the main organizer, so make secondary creators finish possessions.</t>
+          <t>Know the first reference: F. Thomas is a spot-up shooter, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1681,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with M. Tomley, F. Thomas, and G. Silva; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with F. Thomas, G. Silva, and M. Tomley; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1693,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from N. Sa and W. Heinz; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from B. Ferreira and N. Sa; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1717,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially F. Thomas, B. Ferreira, and W. Heinz; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially F. Thomas, B. Ferreira, and M. Tomley; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1753,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose M. Tomley and F. Thomas in help-and-recover situations.</t>
+          <t>Do not lose F. Thomas and G. Silva in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1720,17 +1835,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1740,7 +1855,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1871,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.2</v>
+        <v>29.3</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1776,7 +1891,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1792,17 +1907,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1812,7 +1927,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1828,17 +1943,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="D5" t="n">
-        <v>11.5</v>
+        <v>13.7</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1848,7 +1963,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1864,17 +1979,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26.3</v>
+        <v>25.1</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1900,13 +2015,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="D7" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1915,12 +2030,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1935,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2034,32 +2149,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2080,12 +2195,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2098,11 +2213,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
         <v>1.3</v>
@@ -2126,32 +2241,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2181,23 +2296,23 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2218,36 +2333,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2264,16 +2379,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2282,18 +2397,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2310,16 +2425,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_T._DIAS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>T. Dias</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2328,18 +2443,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2356,12 +2471,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_T._TONEY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>T. Toney</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2374,18 +2489,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -2414,19 +2529,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
     </row>
@@ -2450,19 +2565,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -2486,19 +2601,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -2522,19 +2637,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -2558,19 +2673,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -2602,19 +2717,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2646,19 +2761,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2785,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2686,23 +2801,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2829,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2730,23 +2845,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -2778,19 +2893,107 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAB_C._ROBERT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CAB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,41 +515,41 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -567,16 +567,16 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -586,17 +586,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,26 +619,26 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,41 +671,41 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -723,41 +723,41 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -775,21 +775,21 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -827,41 +827,93 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.0</t>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAB_T._LISBOA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Lisboa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -942,16 +994,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>75.7</v>
+        <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>89.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>73.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="G2" t="n">
-        <v>16.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3">
@@ -962,7 +1014,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -971,74 +1023,74 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>81.7</v>
       </c>
       <c r="E3" t="n">
-        <v>89.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F3" t="n">
-        <v>72.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best net</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F. Thomas | W. Heinz</t>
+          <t>B. Ferreira | F. Thomas | W. Heinz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65.3</v>
       </c>
       <c r="E4" t="n">
-        <v>89.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>72.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best defense</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva</t>
+          <t>F. Thomas | N. Sa</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54.9</v>
+        <v>59.9</v>
       </c>
       <c r="E5" t="n">
-        <v>85.3</v>
+        <v>84.2</v>
       </c>
       <c r="F5" t="n">
-        <v>71.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G5" t="n">
-        <v>13.8</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1158,7 +1210,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (16.1 min)</t>
+          <t>B. Ferreira | F. Thomas | M. Tomley | N. Sa | W. Heinz (18.6 min)</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (39.7 net)</t>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (38.1 net)</t>
         </is>
       </c>
     </row>
@@ -1268,13 +1320,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>-4.2</v>
@@ -1287,16 +1339,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>106.1</v>
+        <v>107.2</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
@@ -1306,16 +1358,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108.3</v>
+        <v>110.7</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5">
@@ -1325,16 +1377,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.1</v>
+        <v>-3.5</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="6">
@@ -1344,16 +1396,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1401,16 +1453,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.7</v>
+        <v>21.5</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -1537,7 +1589,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1769,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially F. Thomas, B. Ferreira, and M. Tomley; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially B. Ferreira, F. Thomas, and M. Tomley; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1835,17 +1887,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34.4</v>
+        <v>31.6</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1871,17 +1923,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1907,17 +1959,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1927,7 +1979,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1995,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="D5" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1963,7 +2015,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>primary scorer</t>
         </is>
       </c>
     </row>
@@ -1979,17 +2031,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="D6" t="n">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2015,17 +2067,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2035,7 +2087,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2210,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2204,20 +2256,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H3" t="n">
         <v>1.3</v>
@@ -2250,20 +2302,20 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -2296,23 +2348,23 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2342,23 +2394,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2388,20 +2440,20 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
         <v>0.6</v>
@@ -2443,11 +2495,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2529,11 +2581,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -2541,7 +2593,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
     </row>
@@ -2565,11 +2617,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -2577,7 +2629,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -2601,19 +2653,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -2637,19 +2689,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -2673,19 +2725,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2749,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2717,19 +2769,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2793,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2761,19 +2813,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -2805,19 +2857,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -2849,19 +2901,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -2893,19 +2945,19 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2989,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2949,7 +3001,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -2977,23 +3029,23 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
